--- a/tasklist/intersteller.xlsx
+++ b/tasklist/intersteller.xlsx
@@ -4,7 +4,7 @@
   <workbookPr date1904="0"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="第1章：エウロパ・ハック（生産基盤）" sheetId="1" state="visible" r:id="rId1"/>
@@ -563,7 +563,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10.000000"/>
       <name val="Noto Sans CJK JP"/>
@@ -588,6 +588,12 @@
       <name val="IPAGothic"/>
     </font>
     <font>
+      <sz val="10.500000"/>
+      <color indexed="2"/>
+      <name val="IPAGothic"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10.500000"/>
       <color indexed="2"/>
       <name val="IPAGothic"/>
@@ -643,7 +649,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -662,25 +668,36 @@
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
       <alignment wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
       <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="9" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="10" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="0">
@@ -1218,20 +1235,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="32.799999999999997">
-      <c r="A4" s="4" t="s">
+    <row r="4" s="5" customFormat="1" ht="32.799999999999997">
+      <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="8" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4423,13 +4440,13 @@
       <c r="C5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="9" t="s">
         <v>42</v>
       </c>
       <c r="G5" s="2"/>
@@ -4469,7 +4486,7 @@
       <c r="E6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="7"/>
+      <c r="F6" s="10"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -32379,94 +32396,94 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="16384" style="8" width="10.28125"/>
+    <col min="1" max="16384" style="11" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="11" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="2" ht="99.75">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="12" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="3" ht="85.5">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="11"/>
     </row>
     <row r="4" ht="57">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="11" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="5" ht="71.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="11" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="6" ht="71.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="11" t="s">
         <v>88</v>
       </c>
     </row>
@@ -32482,162 +32499,162 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="16384" style="8" width="10.28125"/>
+    <col min="1" max="16384" style="11" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="42.75">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" ht="128.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="11" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="3" ht="128.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="13" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="4" ht="114">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="5" ht="85.5">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="11" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="6" ht="114">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="11" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="7" ht="114">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="11" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="8" ht="85.5">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="11" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="9" ht="85.5">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="11" t="s">
         <v>123</v>
       </c>
     </row>
@@ -32718,59 +32735,59 @@
       <c r="D3" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="7" t="s">
         <v>134</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="4" ht="38.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" s="5" customFormat="1" ht="38.25">
+      <c r="A4" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="7" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="5" ht="38.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" s="5" customFormat="1" ht="38.25">
+      <c r="A5" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="7" t="s">
         <v>146</v>
       </c>
     </row>
@@ -32907,7 +32924,7 @@
       <c r="A13" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="B13" s="11"/>
+      <c r="B13" s="14"/>
       <c r="C13" s="2" t="s">
         <v>174</v>
       </c>
